--- a/docs/給与計算100案件_10月完全移行_週間スケジュール.xlsx
+++ b/docs/給与計算100案件_10月完全移行_週間スケジュール.xlsx
@@ -10168,12 +10168,12 @@
       </c>
       <c r="Q31" s="49" t="n"/>
       <c r="R31" s="139">
-        <f>SUM(R25:R30)</f>
+        <f>IF(COUNT(R25:R30)=0,"",SUM(R25:R30))</f>
         <v/>
       </c>
       <c r="S31" s="49" t="n"/>
       <c r="T31" s="140">
-        <f>R31-P31</f>
+        <f>IF(COUNT(R25:R30)=0,"",R31-P31)</f>
         <v/>
       </c>
     </row>
